--- a/Louisiana_SHPO_traits.xlsx
+++ b/Louisiana_SHPO_traits.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jpaige/Desktop/Research repositories/Site_form_codebook/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E26F38E-DA23-6C4C-AD33-D64277649B4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A1EDFBD-A26D-BC4D-89B4-DCE11CB575E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="37140" yWindow="3280" windowWidth="28040" windowHeight="16160" xr2:uid="{58D64529-F5A8-734A-8B1E-79BC65F5D92F}"/>
   </bookViews>
@@ -303,12 +303,25 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -332,8 +345,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -676,13 +691,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="2" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+    <row r="3" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -716,8 +731,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+    <row r="10" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -756,8 +771,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
+    <row r="18" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
     </row>
@@ -831,8 +846,8 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
+    <row r="33" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -991,8 +1006,8 @@
         <v>63</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
+    <row r="65" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="1" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1001,13 +1016,13 @@
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
+    <row r="67" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
+    <row r="68" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="1" t="s">
         <v>67</v>
       </c>
     </row>
